--- a/model/GRG_model_v1.0.xlsx
+++ b/model/GRG_model_v1.0.xlsx
@@ -348,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="697">
   <si>
     <t xml:space="preserve">Greggs plc – forecast summary, FY26–FY28</t>
   </si>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">1. What Greggs does and why I chose it</t>
   </si>
   <si>
-    <t xml:space="preserve">Greggs is the UK's largest food-on-the-go retailer: 2,739 shops at the end of FY25 (2,137 run by Greggs, 602 by franchise partners), revenue of £2.15bn and underlying profit before tax of £171.9m. I chose it because its revenue is driven by things I can see and test (shop openings and like-for-like sales), and it reports trading every quarter, so I can check my forecast against actual results within months.</t>
+    <t xml:space="preserve">Greggs is the UK's largest food-on-the-go retailer: 2,739 shops at the end of FY25 (2,137 run by Greggs, 602 by franchise partners), revenue of £2.15bn and underlying profit before tax of £171.9m. I chose it because its revenue is driven by things I can see and test (shop openings and like-for-like sales), and its next trading update and annual results come within months, so I can check my forecast against actual results.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Key assumptions (base case) and why</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">New-shop % that would explain all of it</t>
   </si>
   <si>
-    <t xml:space="preserve">Fed Greggs' actual FY25 openings and LFL, my revenue method came within 0.4% of actual company-managed revenue. Closing the gap would need new shops to sell 96% of a mature shop rather than my 85%. I kept 85%: many FY25 closures were relocations into bigger units, which the method does not credit. What I learned: the mechanics work; the risk sits in the assumptions.</t>
+    <t xml:space="preserve">Under the back-test assumptions (Greggs' actual FY25 openings and LFL), my revenue method reproduced FY25 company-managed revenue to within 0.4%. Closing the gap would need new shops to sell 96% of a mature shop rather than my 85%. I kept 85%: many FY25 closures were relocations into bigger units, which the method does not credit. This is one test of the method, not proof of predictive accuracy; the live test against FY26 results is the stronger check.</t>
   </si>
   <si>
     <t xml:space="preserve">7. Other simplifications and where the model would break</t>
@@ -699,6 +699,18 @@
   </si>
   <si>
     <t xml:space="preserve">Interim results presentation, 29 Jul 2026 (26 weeks to 27 Jun 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4 2025 trading update, 8 Jan 2026: FY25 franchised shops, openings and closures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3 2026 trading update: third-quarter like-for-like sales growth (supports the FY26 LFL assumption)</t>
   </si>
   <si>
     <t xml:space="preserve">Rule</t>
@@ -2299,7 +2311,7 @@
     <t xml:space="preserve">On the chosen ranges and correlations, FY26 underlying profit beats FY25's £171.9m in about 90% of 10,000 runs (P5–P95: £170m–£190m). That makes growth the most likely outcome under these inputs, not a certainty: the probability depends on the ranges set, and a shock outside them is not captured.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cash stays positive in every run and falls below £50m in about 1% of runs. On these assumptions, falling capex lets Greggs fund openings, restructuring and dividends without new debt, after negative free cash flow in FY25.</t>
+    <t xml:space="preserve">Cash stays positive in every simulated run and falls below £50m in about 1% of runs. On these assumptions, falling capex lets Greggs fund openings, restructuring and dividends without new debt, after negative free cash flow in FY25.</t>
   </si>
   <si>
     <t xml:space="preserve">I would watch like-for-like growth. Margin moves FY28 profit most (a £53m swing across its range), but LFL moves it £23m directly and, through its 0.5 correlation with margin in the simulation, pulls margin with it. LFL has slowed from 17.8% in FY22 to 2.4% in FY25.</t>
@@ -3408,9 +3420,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>591840</xdr:colOff>
+      <xdr:colOff>591480</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>121680</xdr:rowOff>
+      <xdr:rowOff>121320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3424,7 +3436,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11466360" y="1036800"/>
-          <a:ext cx="6095160" cy="3199680"/>
+          <a:ext cx="6094800" cy="3199320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3445,9 +3457,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>591840</xdr:colOff>
+      <xdr:colOff>591480</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>7200</xdr:rowOff>
+      <xdr:rowOff>6840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3461,7 +3473,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11466360" y="4656240"/>
-          <a:ext cx="6095160" cy="2894760"/>
+          <a:ext cx="6094800" cy="2894400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4540,7 +4552,7 @@
     <row r="69" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="33" t="str">
         <f aca="false">"2. "&amp;Simulation!B59</f>
-        <v>2. Cash stays positive in every run and falls below £50m in about 1% of runs. On these assumptions, falling capex lets Greggs fund openings, restructuring and dividends without new debt, after negative free cash flow in FY25.</v>
+        <v>2. Cash stays positive in every simulated run and falls below £50m in about 1% of runs. On these assumptions, falling capex lets Greggs fund openings, restructuring and dividends without new debt, after negative free cash flow in FY25.</v>
       </c>
       <c r="B69" s="33"/>
       <c r="C69" s="33"/>
@@ -4608,12 +4620,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4626,41 +4638,41 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="52" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="131" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B5" s="105" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C5" s="105" t="s">
         <v>49</v>
       </c>
       <c r="D5" s="105" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="E5" s="105" t="s">
         <v>50</v>
       </c>
       <c r="F5" s="105" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="G5" s="105" t="s">
         <v>51</v>
       </c>
       <c r="H5" s="105" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="I5" s="105" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5013,20 +5025,20 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="52" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="131" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="G23" s="105" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="G24" s="19" t="n">
         <v>0.898</v>
@@ -5034,7 +5046,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>0.48</v>
@@ -5042,7 +5054,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>0.867</v>
@@ -5050,7 +5062,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="G27" s="19" t="n">
         <v>0.01</v>
@@ -5058,7 +5070,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>0</v>
@@ -5066,7 +5078,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="52" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5074,19 +5086,19 @@
         <v>8</v>
       </c>
       <c r="D31" s="105" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E31" s="105" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F31" s="105" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G31" s="105" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="H31" s="105" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5191,7 +5203,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D37" s="29" t="n">
         <v>218.5</v>
@@ -5231,7 +5243,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D39" s="29" t="n">
         <v>217.9</v>
@@ -5271,33 +5283,33 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="52" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="131" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B44" s="105" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C44" s="105" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D44" s="105" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E44" s="105" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="F44" s="105" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="G44" s="105" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="H44" s="105" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5380,12 +5392,12 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="52" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="131" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B50" s="105" t="s">
         <v>9</v>
@@ -5399,7 +5411,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B51" s="32" t="n">
         <v>1.7</v>
@@ -5413,7 +5425,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B52" s="32" t="n">
         <v>-1.7</v>
@@ -5427,7 +5439,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B53" s="32" t="n">
         <v>22.8</v>
@@ -5441,7 +5453,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B54" s="32" t="n">
         <v>-22.8</v>
@@ -5455,15 +5467,15 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="52" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="132" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
@@ -5475,10 +5487,10 @@
     </row>
     <row r="59" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="132" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -5490,10 +5502,10 @@
     </row>
     <row r="60" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="132" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
@@ -5536,12 +5548,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5555,25 +5567,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="71" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C4" s="71" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D4" s="71" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E4" s="71" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F4" s="71" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G4" s="71" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H4" s="71" t="s">
         <v>9</v>
@@ -5587,7 +5599,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="60" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B5" s="56" t="s">
         <v>86</v>
@@ -5615,7 +5627,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="60" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B6" s="56" t="s">
         <v>86</v>
@@ -5643,7 +5655,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="60" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B7" s="56" t="s">
         <v>86</v>
@@ -5671,7 +5683,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="60" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B8" s="56" t="s">
         <v>86</v>
@@ -5699,7 +5711,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="60" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B9" s="56" t="s">
         <v>86</v>
@@ -5727,7 +5739,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="60" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B10" s="56" t="s">
         <v>86</v>
@@ -5755,7 +5767,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="60" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B11" s="56" t="s">
         <v>86</v>
@@ -5783,10 +5795,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="60" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C12" s="133" t="n">
         <f aca="false">ROUND(Historical!C77-Historical!C82,1)</f>
@@ -5823,10 +5835,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="60" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C13" s="133" t="n">
         <f aca="false">ROUND(Historical!C113-Historical!C61,1)</f>
@@ -5863,7 +5875,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="60" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B14" s="56" t="s">
         <v>86</v>
@@ -5891,7 +5903,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="60" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B15" s="56" t="s">
         <v>86</v>
@@ -5919,7 +5931,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B16" s="56" t="s">
         <v>86</v>
@@ -5947,7 +5959,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="60" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B17" s="56" t="s">
         <v>86</v>
@@ -5975,7 +5987,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="77" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C19" s="134" t="n">
         <f aca="false">SUMPRODUCT(ABS(C5:G17))</f>
@@ -5984,7 +5996,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="77" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C20" s="62" t="str">
         <f aca="false">IF(C19&lt;0.05,"OK","CHECK")</f>
@@ -5993,12 +6005,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="77" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="60" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B23" s="56" t="s">
         <v>97</v>
@@ -6026,7 +6038,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="60" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B24" s="56" t="s">
         <v>97</v>
@@ -6054,7 +6066,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="60" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B25" s="56" t="s">
         <v>97</v>
@@ -6082,7 +6094,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="60" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B26" s="56" t="s">
         <v>99</v>
@@ -6107,7 +6119,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="60" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B27" s="56" t="s">
         <v>84</v>
@@ -6124,21 +6136,21 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="77" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="47" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B29" s="47" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D29" s="136" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="E29" s="136"/>
       <c r="F29" s="136"/>
@@ -6149,16 +6161,16 @@
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="40" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D30" s="137" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="E30" s="137"/>
       <c r="F30" s="137"/>
@@ -6169,16 +6181,16 @@
     </row>
     <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="40" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C31" s="49" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D31" s="137" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="E31" s="137"/>
       <c r="F31" s="137"/>
@@ -6189,16 +6201,16 @@
     </row>
     <row r="32" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="40" t="s">
+        <v>688</v>
+      </c>
+      <c r="B32" s="49" t="s">
+        <v>689</v>
+      </c>
+      <c r="C32" s="49" t="s">
         <v>684</v>
       </c>
-      <c r="B32" s="49" t="s">
-        <v>685</v>
-      </c>
-      <c r="C32" s="49" t="s">
-        <v>680</v>
-      </c>
       <c r="D32" s="137" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E32" s="137"/>
       <c r="F32" s="137"/>
@@ -6209,16 +6221,16 @@
     </row>
     <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="40" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C33" s="49" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D33" s="137" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E33" s="137"/>
       <c r="F33" s="137"/>
@@ -6229,16 +6241,16 @@
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="40" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C34" s="49" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D34" s="137" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E34" s="137"/>
       <c r="F34" s="137"/>
@@ -6249,16 +6261,16 @@
     </row>
     <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="40" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C35" s="49" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D35" s="137" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="E35" s="137"/>
       <c r="F35" s="137"/>
@@ -6659,22 +6671,30 @@
       <c r="E32" s="44"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="35"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="35"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
+      <c r="A33" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="38" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B35" s="35"/>
       <c r="C35" s="35"/>
@@ -6683,10 +6703,10 @@
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="41" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B36" s="44" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C36" s="44"/>
       <c r="D36" s="44"/>
@@ -6694,10 +6714,10 @@
     </row>
     <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="41" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B37" s="44" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C37" s="44"/>
       <c r="D37" s="44"/>
@@ -6705,10 +6725,10 @@
     </row>
     <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="41" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B38" s="44" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C38" s="44"/>
       <c r="D38" s="44"/>
@@ -6716,10 +6736,10 @@
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="41" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B39" s="44" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C39" s="44"/>
       <c r="D39" s="44"/>
@@ -6727,10 +6747,10 @@
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="41" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B40" s="44" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C40" s="44"/>
       <c r="D40" s="44"/>
@@ -6738,10 +6758,10 @@
     </row>
     <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="41" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B41" s="44" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C41" s="44"/>
       <c r="D41" s="44"/>
@@ -6749,10 +6769,10 @@
     </row>
     <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="41" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B42" s="44" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C42" s="44"/>
       <c r="D42" s="44"/>
@@ -6760,7 +6780,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="38" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B43" s="35"/>
       <c r="C43" s="35"/>
@@ -6769,10 +6789,10 @@
     </row>
     <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="41" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B44" s="44" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C44" s="44"/>
       <c r="D44" s="44"/>
@@ -6780,10 +6800,10 @@
     </row>
     <row r="45" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="41" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B45" s="44" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C45" s="44"/>
       <c r="D45" s="44"/>
@@ -6791,10 +6811,10 @@
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="41" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B46" s="44" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C46" s="44"/>
       <c r="D46" s="44"/>
@@ -6802,10 +6822,10 @@
     </row>
     <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="41" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B47" s="44" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C47" s="44"/>
       <c r="D47" s="44"/>
@@ -6813,10 +6833,10 @@
     </row>
     <row r="48" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="36" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C48" s="45"/>
       <c r="D48" s="45"/>
@@ -6831,7 +6851,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="38" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B50" s="35"/>
       <c r="C50" s="35"/>
@@ -6840,31 +6860,31 @@
     </row>
     <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="46" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B51" s="47" t="s">
         <v>59</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D51" s="47" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E51" s="48"/>
     </row>
     <row r="52" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B52" s="50" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C52" s="49" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E52" s="51"/>
     </row>
@@ -6873,13 +6893,13 @@
         <v>13</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D53" s="49" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E53" s="35"/>
     </row>
@@ -6888,27 +6908,27 @@
         <v>15</v>
       </c>
       <c r="B54" s="49" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" s="49" t="s">
         <v>157</v>
       </c>
-      <c r="B55" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="C55" s="49" t="s">
-        <v>153</v>
-      </c>
       <c r="D55" s="49" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6916,41 +6936,41 @@
         <v>19</v>
       </c>
       <c r="B56" s="49" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C56" s="49" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D56" s="49" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="49" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D57" s="49" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B58" s="49" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D58" s="49" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6958,55 +6978,55 @@
         <v>23</v>
       </c>
       <c r="B59" s="49" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B60" s="49" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D60" s="49" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="49" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B61" s="49" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="49" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B62" s="49" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D62" s="49" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7014,51 +7034,51 @@
         <v>27</v>
       </c>
       <c r="B63" s="49" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D63" s="49" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B65" s="49" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C65" s="49" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="52" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="8" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
@@ -7066,7 +7086,7 @@
     </row>
     <row r="69" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="8" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
@@ -7074,7 +7094,7 @@
     </row>
     <row r="70" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -7082,7 +7102,7 @@
     </row>
     <row r="71" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
@@ -7090,14 +7110,14 @@
     </row>
     <row r="72" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="38">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B15:E15"/>
@@ -7117,6 +7137,8 @@
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="B38:E38"/>
@@ -7160,12 +7182,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7176,7 +7198,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="53" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7184,47 +7206,47 @@
         <v>30</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D4" s="55" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F4" s="55" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G4" s="55" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="56" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G5" s="57" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B6" s="59"/>
       <c r="C6" s="59"/>
@@ -7238,7 +7260,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C7" s="61" t="n">
         <v>1229.7</v>
@@ -7258,10 +7280,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="60" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C8" s="61" t="n">
         <v>-447.7</v>
@@ -7281,10 +7303,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="62" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C9" s="63" t="n">
         <f aca="false">C7+C8</f>
@@ -7309,10 +7331,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="60" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>213</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>209</v>
       </c>
       <c r="C10" s="61" t="n">
         <v>-567.6</v>
@@ -7332,10 +7354,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="60" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C11" s="61" t="n">
         <v>-61.2</v>
@@ -7355,10 +7377,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="60" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C12" s="61" t="n">
         <v>0</v>
@@ -7378,10 +7400,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="62" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="56" t="s">
         <v>216</v>
-      </c>
-      <c r="B13" s="56" t="s">
-        <v>212</v>
       </c>
       <c r="C13" s="63" t="n">
         <f aca="false">C9+C10+C11+C12</f>
@@ -7406,10 +7428,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="60" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C14" s="61" t="n">
         <v>0</v>
@@ -7429,10 +7451,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="60" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B15" s="56" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C15" s="61" t="n">
         <v>-7.6</v>
@@ -7452,10 +7474,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="62" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C16" s="63" t="n">
         <f aca="false">C13+C14+C15</f>
@@ -7480,10 +7502,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="60" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C17" s="61" t="n">
         <v>-28.1</v>
@@ -7503,10 +7525,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="62" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C18" s="63" t="n">
         <f aca="false">C16+C17</f>
@@ -7531,7 +7553,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B20" s="59"/>
       <c r="C20" s="59"/>
@@ -7542,10 +7564,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="60" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C21" s="61" t="n">
         <v>0</v>
@@ -7565,10 +7587,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="60" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C22" s="61" t="n">
         <v>0</v>
@@ -7588,10 +7610,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="60" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C23" s="61" t="n">
         <v>0</v>
@@ -7614,7 +7636,7 @@
         <v>33</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C24" s="63" t="n">
         <f aca="false">C13-C21</f>
@@ -7642,7 +7664,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C25" s="63" t="n">
         <f aca="false">C16-C21-C22</f>
@@ -7670,7 +7692,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C26" s="64" t="n">
         <f aca="false">IF(C7=0,0,C24/C7)</f>
@@ -7695,10 +7717,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="60" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C27" s="64" t="n">
         <f aca="false">IF(C16=0,0,-C17/C16)</f>
@@ -7723,7 +7745,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="58" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B29" s="59"/>
       <c r="C29" s="59"/>
@@ -7734,10 +7756,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="60" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C30" s="61" t="n">
         <v>153.2</v>
@@ -7757,10 +7779,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="60" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C31" s="61" t="n">
         <v>145.6</v>
@@ -7780,10 +7802,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="60" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C32" s="61" t="n">
         <v>117.5</v>
@@ -7803,10 +7825,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="60" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C33" s="61" t="n">
         <v>145.6</v>
@@ -7826,7 +7848,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="58" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B35" s="59"/>
       <c r="C35" s="59"/>
@@ -7837,10 +7859,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="60" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C36" s="61" t="n">
         <v>1098.2</v>
@@ -7860,10 +7882,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="60" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C37" s="61" t="n">
         <v>131.5</v>
@@ -7883,10 +7905,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="60" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C38" s="65" t="n">
         <f aca="false">C36+C37-C7</f>
@@ -7911,10 +7933,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="60" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C39" s="66" t="n">
         <v>2078</v>
@@ -7938,10 +7960,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="60" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C40" s="66" t="n">
         <v>2181</v>
@@ -7961,10 +7983,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="60" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C41" s="66" t="n">
         <v>375</v>
@@ -7984,10 +8006,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="60" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B42" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C42" s="67" t="n">
         <f aca="false">IF(C41="","",C40-C41)</f>
@@ -8012,10 +8034,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="60" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B43" s="56" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C43" s="66" t="n">
         <v>131</v>
@@ -8035,10 +8057,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="60" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B44" s="56" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C44" s="66" t="n">
         <v>-28</v>
@@ -8058,10 +8080,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="60" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B45" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C45" s="67" t="n">
         <f aca="false">C40-C39</f>
@@ -8086,10 +8108,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="60" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B46" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C46" s="67" t="n">
         <f aca="false">IF(C43="",0,C43+C44-C45)</f>
@@ -8114,10 +8136,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="60" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B47" s="56" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C47" s="68" t="n">
         <v>0.524</v>
@@ -8137,10 +8159,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="60" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B48" s="56" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C48" s="69"/>
       <c r="D48" s="69"/>
@@ -8156,10 +8178,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="60" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B49" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C49" s="70" t="n">
         <f aca="false">IF(C42="","",C36/C42)</f>
@@ -8184,7 +8206,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="58" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B51" s="59"/>
       <c r="C51" s="59"/>
@@ -8195,10 +8217,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="60" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B52" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C52" s="61" t="n">
         <v>14.9</v>
@@ -8218,10 +8240,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="60" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B53" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C53" s="61" t="n">
         <v>343.8</v>
@@ -8241,10 +8263,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="60" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B54" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C54" s="61" t="n">
         <v>263.6</v>
@@ -8264,10 +8286,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="60" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B55" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C55" s="61" t="n">
         <v>0</v>
@@ -8287,10 +8309,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="62" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B56" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C56" s="63" t="n">
         <f aca="false">SUM(C52:C55)</f>
@@ -8315,10 +8337,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="60" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B57" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C57" s="61" t="n">
         <v>27.9</v>
@@ -8338,10 +8360,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="60" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B58" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C58" s="61" t="n">
         <v>37.6</v>
@@ -8361,10 +8383,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="60" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B59" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C59" s="61" t="n">
         <v>1.6</v>
@@ -8384,10 +8406,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="60" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B60" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C60" s="61" t="n">
         <v>0.4</v>
@@ -8407,10 +8429,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="60" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B61" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C61" s="61" t="n">
         <v>198.6</v>
@@ -8430,10 +8452,10 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="62" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B62" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C62" s="63" t="n">
         <f aca="false">SUM(C57:C61)</f>
@@ -8458,10 +8480,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="62" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B63" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C63" s="63" t="n">
         <f aca="false">C56+C62</f>
@@ -8486,10 +8508,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="60" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B64" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C64" s="61" t="n">
         <v>-153.4</v>
@@ -8509,10 +8531,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="60" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B65" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C65" s="61" t="n">
         <v>0</v>
@@ -8532,10 +8554,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="60" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B66" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C66" s="61" t="n">
         <v>-49.3</v>
@@ -8555,10 +8577,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="60" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B67" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C67" s="61" t="n">
         <v>-4.2</v>
@@ -8578,10 +8600,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="62" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B68" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C68" s="63" t="n">
         <f aca="false">SUM(C64:C67)</f>
@@ -8606,10 +8628,10 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="60" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B69" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C69" s="61" t="n">
         <v>0</v>
@@ -8629,10 +8651,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="60" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C70" s="61" t="n">
         <v>-3.2</v>
@@ -8652,10 +8674,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="60" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B71" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C71" s="61" t="n">
         <v>-233.9</v>
@@ -8675,10 +8697,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="60" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C72" s="61" t="n">
         <v>-10</v>
@@ -8698,10 +8720,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="60" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B73" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C73" s="61" t="n">
         <v>-2.8</v>
@@ -8721,10 +8743,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="60" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B74" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C74" s="61" t="n">
         <v>-2.4</v>
@@ -8744,10 +8766,10 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="62" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B75" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C75" s="63" t="n">
         <f aca="false">SUM(C69:C74)</f>
@@ -8772,10 +8794,10 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="62" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B76" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C76" s="63" t="n">
         <f aca="false">C68+C75</f>
@@ -8800,10 +8822,10 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="62" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B77" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C77" s="63" t="n">
         <f aca="false">C63+C76</f>
@@ -8828,10 +8850,10 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="60" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B78" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C78" s="61" t="n">
         <v>2</v>
@@ -8851,10 +8873,10 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="60" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B79" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C79" s="61" t="n">
         <v>20</v>
@@ -8874,10 +8896,10 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="60" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B80" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C80" s="61" t="n">
         <v>0.4</v>
@@ -8897,10 +8919,10 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="60" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B81" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C81" s="61" t="n">
         <v>406.8</v>
@@ -8920,10 +8942,10 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="62" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B82" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C82" s="63" t="n">
         <f aca="false">SUM(C78:C81)</f>
@@ -8948,10 +8970,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="60" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B83" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C83" s="61" t="n">
         <v>888.4</v>
@@ -8971,10 +8993,10 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="60" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B84" s="56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C84" s="61" t="n">
         <v>429.2</v>
@@ -8994,7 +9016,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="58" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B86" s="59"/>
       <c r="C86" s="59"/>
@@ -9005,10 +9027,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="60" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B87" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C87" s="65" t="n">
         <f aca="false">C61+C69</f>
@@ -9033,10 +9055,10 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="60" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B88" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C88" s="65" t="n">
         <f aca="false">C66+C71</f>
@@ -9061,10 +9083,10 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="60" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B89" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C89" s="65" t="n">
         <f aca="false">C87+C88</f>
@@ -9089,7 +9111,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="58" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B91" s="59"/>
       <c r="C91" s="59"/>
@@ -9100,10 +9122,10 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="60" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B92" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C92" s="61" t="n">
         <v>312.1</v>
@@ -9123,10 +9145,10 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="60" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B93" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C93" s="61" t="n">
         <v>-19.2</v>
@@ -9146,10 +9168,10 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="60" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B94" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C94" s="61" t="n">
         <v>0</v>
@@ -9169,10 +9191,10 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="60" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B95" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C95" s="61" t="n">
         <v>-6.3</v>
@@ -9192,10 +9214,10 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="60" t="s">
+        <v>306</v>
+      </c>
+      <c r="B96" s="56" t="s">
         <v>302</v>
-      </c>
-      <c r="B96" s="56" t="s">
-        <v>298</v>
       </c>
       <c r="C96" s="61" t="n">
         <v>-1.1</v>
@@ -9215,10 +9237,10 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="62" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B97" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C97" s="63" t="n">
         <f aca="false">SUM(C92:C96)</f>
@@ -9243,10 +9265,10 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="60" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B98" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C98" s="61" t="n">
         <v>-50.5</v>
@@ -9266,10 +9288,10 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="60" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B99" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C99" s="61" t="n">
         <v>-3.8</v>
@@ -9289,10 +9311,10 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="60" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B100" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C100" s="61" t="n">
         <v>0.3</v>
@@ -9312,10 +9334,10 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="60" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B101" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C101" s="61" t="n">
         <v>0</v>
@@ -9335,10 +9357,10 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="62" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B102" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C102" s="63" t="n">
         <f aca="false">SUM(C98:C101)</f>
@@ -9363,10 +9385,10 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="60" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B103" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C103" s="61" t="n">
         <v>0</v>
@@ -9386,10 +9408,10 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="60" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B104" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C104" s="61" t="n">
         <v>0</v>
@@ -9409,10 +9431,10 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="60" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B105" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C105" s="61" t="n">
         <v>4.3</v>
@@ -9432,10 +9454,10 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="60" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B106" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C106" s="61" t="n">
         <v>0.3</v>
@@ -9455,10 +9477,10 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="60" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B107" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C107" s="61" t="n">
         <v>-10</v>
@@ -9478,10 +9500,10 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="60" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B108" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C108" s="61" t="n">
         <v>-15.3</v>
@@ -9501,10 +9523,10 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="60" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B109" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C109" s="61" t="n">
         <v>-49</v>
@@ -9524,10 +9546,10 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="62" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B110" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C110" s="63" t="n">
         <f aca="false">SUM(C103:C109)</f>
@@ -9552,10 +9574,10 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="62" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B111" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C111" s="63" t="n">
         <f aca="false">C97+C102+C110</f>
@@ -9580,10 +9602,10 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="60" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B112" s="56" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C112" s="61" t="n">
         <v>36.8</v>
@@ -9607,10 +9629,10 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="62" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B113" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C113" s="63" t="n">
         <f aca="false">C112+C111</f>
@@ -9635,10 +9657,10 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="60" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B114" s="56" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C114" s="61" t="n">
         <v>161.8</v>
@@ -9658,7 +9680,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="58" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B116" s="59"/>
       <c r="C116" s="59"/>
@@ -9669,10 +9691,10 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="60" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B117" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C117" s="65" t="n">
         <f aca="false">C98+C99</f>
@@ -9700,7 +9722,7 @@
         <v>36</v>
       </c>
       <c r="B118" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C118" s="65" t="n">
         <f aca="false">C97+C117+C109</f>
@@ -9725,7 +9747,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="58" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B120" s="59"/>
       <c r="C120" s="59"/>
@@ -9736,10 +9758,10 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="60" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B121" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C121" s="61" t="n">
         <v>117.5</v>
@@ -9759,10 +9781,10 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="60" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B122" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C122" s="61" t="n">
         <v>4.5</v>
@@ -9782,10 +9804,10 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="60" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B123" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C123" s="61" t="n">
         <v>54.2</v>
@@ -9805,10 +9827,10 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="60" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B124" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C124" s="61" t="n">
         <v>48.7</v>
@@ -9828,10 +9850,10 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="B125" s="56" t="s">
         <v>329</v>
-      </c>
-      <c r="B125" s="56" t="s">
-        <v>325</v>
       </c>
       <c r="C125" s="61" t="n">
         <v>-1.9</v>
@@ -9851,10 +9873,10 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="60" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B126" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C126" s="61" t="n">
         <v>-1.6</v>
@@ -9874,10 +9896,10 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="60" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B127" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C127" s="61" t="n">
         <v>0.9</v>
@@ -9897,10 +9919,10 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="60" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B128" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C128" s="61" t="n">
         <v>-0.5</v>
@@ -9920,10 +9942,10 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="60" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B129" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C129" s="61" t="n">
         <v>2.2</v>
@@ -9943,10 +9965,10 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="60" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B130" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C130" s="61" t="n">
         <v>0</v>
@@ -9966,10 +9988,10 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="60" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B131" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C131" s="61" t="n">
         <v>7.6</v>
@@ -9989,10 +10011,10 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="60" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B132" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C132" s="61" t="n">
         <v>28.1</v>
@@ -10012,10 +10034,10 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="60" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B133" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C133" s="61" t="n">
         <v>-5.4</v>
@@ -10035,10 +10057,10 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="60" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B134" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C134" s="61" t="n">
         <v>1.8</v>
@@ -10058,10 +10080,10 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="60" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B135" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C135" s="61" t="n">
         <v>58.9</v>
@@ -10081,10 +10103,10 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="60" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B136" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C136" s="61" t="n">
         <v>-0.4</v>
@@ -10104,10 +10126,10 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="60" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B137" s="56" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C137" s="61" t="n">
         <v>-2.5</v>
@@ -10127,10 +10149,10 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="62" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B138" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C138" s="63" t="n">
         <f aca="false">SUM(C121:C137)</f>
@@ -10155,10 +10177,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="60" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B139" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C139" s="65" t="n">
         <f aca="false">C122+C123+C124</f>
@@ -10212,12 +10234,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10227,13 +10249,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="71" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C4" s="71" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D4" s="71" t="s">
         <v>9</v>
@@ -10247,7 +10269,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B5" s="59"/>
       <c r="C5" s="59"/>
@@ -10257,10 +10279,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="60" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B6" s="72" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D6" s="67" t="n">
         <f aca="false">C8</f>
@@ -10277,10 +10299,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="60" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B7" s="72" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C7" s="73" t="n">
         <f aca="false">Historical!G42-Historical!F42</f>
@@ -10301,10 +10323,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="60" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B8" s="72" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C8" s="73" t="n">
         <f aca="false">Historical!G42</f>
@@ -10325,7 +10347,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="58" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B9" s="59"/>
       <c r="C9" s="59"/>
@@ -10338,7 +10360,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C10" s="74" t="n">
         <f aca="false">Historical!G47</f>
@@ -10359,10 +10381,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="60" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B11" s="72" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C11" s="75" t="n">
         <f aca="false">Historical!G49</f>
@@ -10386,7 +10408,7 @@
         <v>19</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D12" s="64" t="n">
         <f aca="false">Drivers!C9</f>
@@ -10403,7 +10425,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="58" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B13" s="59"/>
       <c r="C13" s="59"/>
@@ -10413,10 +10435,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="60" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B14" s="72" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D14" s="65" t="n">
         <f aca="false">C17*(1+D10)</f>
@@ -10433,10 +10455,10 @@
     </row>
     <row r="15" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="60" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B15" s="72" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D15" s="65" t="n">
         <f aca="false">C7*(1-Drivers!C36)*D11*D12</f>
@@ -10453,10 +10475,10 @@
     </row>
     <row r="16" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B16" s="72" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D16" s="65" t="n">
         <f aca="false">D7*Drivers!C36*D11*D12</f>
@@ -10473,10 +10495,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="62" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B17" s="72" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C17" s="76" t="n">
         <f aca="false">Historical!G36</f>
@@ -10497,10 +10519,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B18" s="72" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C18" s="76" t="n">
         <f aca="false">Historical!G37</f>
@@ -10521,10 +10543,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="62" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B19" s="72" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C19" s="76" t="n">
         <f aca="false">Historical!G7</f>
@@ -10545,10 +10567,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="60" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B20" s="72" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D20" s="64" t="n">
         <f aca="false">(D19/C19)-1</f>
@@ -10565,7 +10587,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="58" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B21" s="59"/>
       <c r="C21" s="59"/>
@@ -10575,10 +10597,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="60" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B22" s="72" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D22" s="67" t="n">
         <f aca="false">IF(D8="","",D8-Forecast!H42)</f>
@@ -10595,15 +10617,15 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="60" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B25" s="72" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C25" s="68" t="n">
         <v>0.072</v>
@@ -10611,10 +10633,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="60" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B26" s="72" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C26" s="61" t="n">
         <v>2305.8</v>
@@ -10622,7 +10644,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="60" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D27" s="64" t="n">
         <f aca="false">IF(D19="","",D19/C26-1)</f>
@@ -10658,12 +10680,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10677,7 +10699,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="56" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10685,22 +10707,22 @@
         <v>30</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D4" s="55" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F4" s="55" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G4" s="55" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H4" s="55" t="s">
         <v>9</v>
@@ -10714,7 +10736,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B6" s="59"/>
       <c r="C6" s="59"/>
@@ -10731,7 +10753,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C7" s="76" t="n">
         <f aca="false">Historical!C7</f>
@@ -10768,7 +10790,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="60" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C8" s="76" t="n">
         <f aca="false">Historical!C8</f>
@@ -10805,7 +10827,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="62" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C9" s="76" t="n">
         <f aca="false">Historical!C9</f>
@@ -10842,7 +10864,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="60" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C10" s="76" t="n">
         <f aca="false">Historical!C10</f>
@@ -10879,7 +10901,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="60" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C11" s="76" t="n">
         <f aca="false">Historical!C11</f>
@@ -10916,7 +10938,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="60" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C12" s="76" t="n">
         <f aca="false">Historical!C12</f>
@@ -10953,7 +10975,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="62" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C13" s="76" t="n">
         <f aca="false">Historical!C13</f>
@@ -10990,7 +11012,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="60" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C14" s="76" t="n">
         <f aca="false">Historical!C14</f>
@@ -11027,7 +11049,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="60" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C15" s="76" t="n">
         <f aca="false">Historical!C15</f>
@@ -11064,7 +11086,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="62" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C16" s="76" t="n">
         <f aca="false">Historical!C16</f>
@@ -11101,10 +11123,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="60" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C17" s="76" t="n">
         <f aca="false">Historical!C17</f>
@@ -11141,7 +11163,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="62" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C18" s="76" t="n">
         <f aca="false">Historical!C18</f>
@@ -11178,7 +11200,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B20" s="59"/>
       <c r="C20" s="59"/>
@@ -11192,10 +11214,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="60" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C21" s="76" t="n">
         <f aca="false">Historical!C21</f>
@@ -11232,7 +11254,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="60" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C22" s="76" t="n">
         <f aca="false">Historical!C22</f>
@@ -11269,7 +11291,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="60" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C23" s="76" t="n">
         <f aca="false">Historical!C23</f>
@@ -11309,7 +11331,7 @@
         <v>33</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C24" s="76" t="n">
         <f aca="false">Historical!C24</f>
@@ -11420,7 +11442,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="60" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C27" s="74" t="n">
         <f aca="false">Historical!C27</f>
@@ -11457,7 +11479,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="58" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B29" s="59"/>
       <c r="C29" s="59"/>
@@ -11471,7 +11493,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="60" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C30" s="76" t="n">
         <f aca="false">Historical!C30</f>
@@ -11499,7 +11521,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="60" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C31" s="76" t="n">
         <f aca="false">Historical!C31</f>
@@ -11527,7 +11549,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="60" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C32" s="76" t="n">
         <f aca="false">Historical!C32</f>
@@ -11555,7 +11577,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="60" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C33" s="76" t="n">
         <f aca="false">Historical!C33</f>
@@ -11583,7 +11605,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="58" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B35" s="59"/>
       <c r="C35" s="59"/>
@@ -11597,10 +11619,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="60" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C36" s="76" t="n">
         <f aca="false">Historical!C36</f>
@@ -11637,10 +11659,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="60" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C37" s="76" t="n">
         <f aca="false">Historical!C37</f>
@@ -11677,7 +11699,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="60" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C38" s="76" t="n">
         <f aca="false">Historical!C38</f>
@@ -11714,7 +11736,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="60" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C39" s="73" t="n">
         <f aca="false">Historical!C39</f>
@@ -11751,10 +11773,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="60" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C40" s="73" t="n">
         <f aca="false">Historical!C40</f>
@@ -11791,7 +11813,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="60" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C41" s="73" t="n">
         <f aca="false">Historical!C41</f>
@@ -11828,7 +11850,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="60" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C42" s="73" t="n">
         <f aca="false">Historical!C42</f>
@@ -11865,7 +11887,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="60" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C43" s="73" t="n">
         <f aca="false">Historical!C43</f>
@@ -11893,7 +11915,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="60" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C44" s="73" t="n">
         <f aca="false">Historical!C44</f>
@@ -11921,7 +11943,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="60" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C45" s="73" t="n">
         <f aca="false">Historical!C45</f>
@@ -11958,7 +11980,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="60" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C46" s="73" t="n">
         <f aca="false">Historical!C46</f>
@@ -11995,7 +12017,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="60" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C47" s="74" t="n">
         <f aca="false">Historical!C47</f>
@@ -12032,7 +12054,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="60" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C48" s="74" t="n">
         <f aca="false">Historical!C48</f>
@@ -12060,7 +12082,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="60" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C49" s="75" t="n">
         <f aca="false">Historical!C49</f>
@@ -12097,7 +12119,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="58" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B51" s="59"/>
       <c r="C51" s="59"/>
@@ -12111,7 +12133,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="60" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C52" s="76" t="n">
         <f aca="false">Historical!C52</f>
@@ -12148,10 +12170,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="60" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B53" s="56" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C53" s="76" t="n">
         <f aca="false">Historical!C53</f>
@@ -12188,10 +12210,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="60" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B54" s="56" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C54" s="76" t="n">
         <f aca="false">Historical!C54</f>
@@ -12228,7 +12250,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="60" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C55" s="76" t="n">
         <f aca="false">Historical!C55</f>
@@ -12265,7 +12287,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="62" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C56" s="76" t="n">
         <f aca="false">Historical!C56</f>
@@ -12302,10 +12324,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="60" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B57" s="56" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C57" s="76" t="n">
         <f aca="false">Historical!C57</f>
@@ -12342,10 +12364,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="60" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B58" s="56" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C58" s="76" t="n">
         <f aca="false">Historical!C58</f>
@@ -12382,7 +12404,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="60" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C59" s="76" t="n">
         <f aca="false">Historical!C59</f>
@@ -12419,7 +12441,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="60" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C60" s="76" t="n">
         <f aca="false">Historical!C60</f>
@@ -12456,10 +12478,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="60" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B61" s="56" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C61" s="76" t="n">
         <f aca="false">Historical!C61</f>
@@ -12496,7 +12518,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="62" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C62" s="76" t="n">
         <f aca="false">Historical!C62</f>
@@ -12533,7 +12555,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="62" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C63" s="76" t="n">
         <f aca="false">Historical!C63</f>
@@ -12570,10 +12592,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="60" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B64" s="56" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C64" s="76" t="n">
         <f aca="false">Historical!C64</f>
@@ -12610,7 +12632,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="60" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C65" s="76" t="n">
         <f aca="false">Historical!C65</f>
@@ -12647,10 +12669,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="60" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B66" s="56" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C66" s="76" t="n">
         <f aca="false">Historical!C66</f>
@@ -12687,7 +12709,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="60" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C67" s="76" t="n">
         <f aca="false">Historical!C67</f>
@@ -12724,7 +12746,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="62" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C68" s="76" t="n">
         <f aca="false">Historical!C68</f>
@@ -12761,7 +12783,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="60" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C69" s="76" t="n">
         <f aca="false">Historical!C69</f>
@@ -12798,7 +12820,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="60" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C70" s="76" t="n">
         <f aca="false">Historical!C70</f>
@@ -12835,10 +12857,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="60" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B71" s="56" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C71" s="76" t="n">
         <f aca="false">Historical!C71</f>
@@ -12875,7 +12897,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="60" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C72" s="76" t="n">
         <f aca="false">Historical!C72</f>
@@ -12912,7 +12934,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="60" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C73" s="76" t="n">
         <f aca="false">Historical!C73</f>
@@ -12949,7 +12971,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="60" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C74" s="76" t="n">
         <f aca="false">Historical!C74</f>
@@ -12986,7 +13008,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="62" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C75" s="76" t="n">
         <f aca="false">Historical!C75</f>
@@ -13023,7 +13045,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="62" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C76" s="76" t="n">
         <f aca="false">Historical!C76</f>
@@ -13060,7 +13082,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="62" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C77" s="76" t="n">
         <f aca="false">Historical!C77</f>
@@ -13097,7 +13119,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="60" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C78" s="76" t="n">
         <f aca="false">Historical!C78</f>
@@ -13134,7 +13156,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="60" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C79" s="76" t="n">
         <f aca="false">Historical!C79</f>
@@ -13171,7 +13193,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="60" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C80" s="76" t="n">
         <f aca="false">Historical!C80</f>
@@ -13208,10 +13230,10 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="60" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B81" s="56" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C81" s="76" t="n">
         <f aca="false">Historical!C81</f>
@@ -13248,7 +13270,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="62" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C82" s="76" t="n">
         <f aca="false">Historical!C82</f>
@@ -13285,7 +13307,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="60" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C83" s="76" t="n">
         <f aca="false">Historical!C83</f>
@@ -13313,7 +13335,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="60" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C84" s="76" t="n">
         <f aca="false">Historical!C84</f>
@@ -13341,7 +13363,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="58" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B86" s="59"/>
       <c r="C86" s="59"/>
@@ -13355,7 +13377,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="60" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C87" s="76" t="n">
         <f aca="false">Historical!C87</f>
@@ -13392,7 +13414,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="60" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C88" s="76" t="n">
         <f aca="false">Historical!C88</f>
@@ -13429,7 +13451,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="60" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C89" s="76" t="n">
         <f aca="false">Historical!C89</f>
@@ -13466,7 +13488,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="58" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B91" s="59"/>
       <c r="C91" s="59"/>
@@ -13480,7 +13502,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="60" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C92" s="76" t="n">
         <f aca="false">Historical!C92</f>
@@ -13517,7 +13539,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="60" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C93" s="76" t="n">
         <f aca="false">Historical!C93</f>
@@ -13554,7 +13576,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="60" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C94" s="76" t="n">
         <f aca="false">Historical!C94</f>
@@ -13591,7 +13613,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="60" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C95" s="76" t="n">
         <f aca="false">Historical!C95</f>
@@ -13628,7 +13650,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="60" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C96" s="76" t="n">
         <f aca="false">Historical!C96</f>
@@ -13665,10 +13687,10 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="62" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B97" s="56" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C97" s="76" t="n">
         <f aca="false">Historical!C97</f>
@@ -13705,7 +13727,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="60" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C98" s="76" t="n">
         <f aca="false">Historical!C98</f>
@@ -13742,7 +13764,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="60" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C99" s="76" t="n">
         <f aca="false">Historical!C99</f>
@@ -13779,7 +13801,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="60" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C100" s="76" t="n">
         <f aca="false">Historical!C100</f>
@@ -13816,7 +13838,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="60" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C101" s="76" t="n">
         <f aca="false">Historical!C101</f>
@@ -13853,7 +13875,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="62" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C102" s="76" t="n">
         <f aca="false">Historical!C102</f>
@@ -13890,7 +13912,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="60" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C103" s="76" t="n">
         <f aca="false">Historical!C103</f>
@@ -13927,7 +13949,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="60" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C104" s="76" t="n">
         <f aca="false">Historical!C104</f>
@@ -13964,7 +13986,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="60" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C105" s="76" t="n">
         <f aca="false">Historical!C105</f>
@@ -14001,7 +14023,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="60" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C106" s="76" t="n">
         <f aca="false">Historical!C106</f>
@@ -14038,7 +14060,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="60" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C107" s="76" t="n">
         <f aca="false">Historical!C107</f>
@@ -14075,10 +14097,10 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="60" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B108" s="56" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C108" s="76" t="n">
         <f aca="false">Historical!C108</f>
@@ -14115,7 +14137,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="60" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C109" s="76" t="n">
         <f aca="false">Historical!C109</f>
@@ -14152,7 +14174,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="62" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C110" s="76" t="n">
         <f aca="false">Historical!C110</f>
@@ -14189,7 +14211,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="62" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C111" s="76" t="n">
         <f aca="false">Historical!C111</f>
@@ -14226,7 +14248,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="60" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C112" s="76" t="n">
         <f aca="false">Historical!C112</f>
@@ -14263,7 +14285,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="62" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C113" s="76" t="n">
         <f aca="false">Historical!C113</f>
@@ -14300,7 +14322,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="60" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C114" s="76" t="n">
         <f aca="false">Historical!C114</f>
@@ -14328,7 +14350,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="58" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B116" s="59"/>
       <c r="C116" s="59"/>
@@ -14342,7 +14364,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="60" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C117" s="76" t="n">
         <f aca="false">Historical!C117</f>
@@ -14416,7 +14438,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="58" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B120" s="59"/>
       <c r="C120" s="59"/>
@@ -14430,7 +14452,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="60" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C121" s="76" t="n">
         <f aca="false">Historical!C121</f>
@@ -14458,7 +14480,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="60" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C122" s="76" t="n">
         <f aca="false">Historical!C122</f>
@@ -14486,7 +14508,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="60" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C123" s="76" t="n">
         <f aca="false">Historical!C123</f>
@@ -14514,7 +14536,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="60" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C124" s="76" t="n">
         <f aca="false">Historical!C124</f>
@@ -14542,7 +14564,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="60" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C125" s="76" t="n">
         <f aca="false">Historical!C125</f>
@@ -14570,7 +14592,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="60" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C126" s="76" t="n">
         <f aca="false">Historical!C126</f>
@@ -14598,7 +14620,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="60" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C127" s="76" t="n">
         <f aca="false">Historical!C127</f>
@@ -14626,7 +14648,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="60" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C128" s="76" t="n">
         <f aca="false">Historical!C128</f>
@@ -14654,7 +14676,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="60" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C129" s="76" t="n">
         <f aca="false">Historical!C129</f>
@@ -14682,7 +14704,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="60" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C130" s="76" t="n">
         <f aca="false">Historical!C130</f>
@@ -14710,7 +14732,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="60" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C131" s="76" t="n">
         <f aca="false">Historical!C131</f>
@@ -14738,7 +14760,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="60" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C132" s="76" t="n">
         <f aca="false">Historical!C132</f>
@@ -14766,7 +14788,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="60" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C133" s="76" t="n">
         <f aca="false">Historical!C133</f>
@@ -14794,7 +14816,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="60" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C134" s="76" t="n">
         <f aca="false">Historical!C134</f>
@@ -14822,7 +14844,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="60" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C135" s="76" t="n">
         <f aca="false">Historical!C135</f>
@@ -14850,7 +14872,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="60" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C136" s="76" t="n">
         <f aca="false">Historical!C136</f>
@@ -14878,7 +14900,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="60" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C137" s="76" t="n">
         <f aca="false">Historical!C137</f>
@@ -14906,7 +14928,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="62" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C138" s="76" t="n">
         <f aca="false">Historical!C138</f>
@@ -14943,7 +14965,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="60" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C139" s="76" t="n">
         <f aca="false">Historical!C139</f>
@@ -14980,7 +15002,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="58" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B141" s="59"/>
       <c r="C141" s="59"/>
@@ -14994,7 +15016,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="60" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="H142" s="65" t="n">
         <f aca="false">Drivers!$C$15*Drivers!$C$27</f>
@@ -15011,7 +15033,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="60" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H143" s="65" t="n">
         <f aca="false">Drivers!$C$15-H142</f>
@@ -15028,7 +15050,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="60" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H144" s="65" t="n">
         <f aca="false">G52*Drivers!$C$28</f>
@@ -15045,7 +15067,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="60" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="H145" s="65" t="n">
         <f aca="false">G53*Drivers!$C$26</f>
@@ -15062,10 +15084,10 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="60" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B146" s="56" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H146" s="65" t="n">
         <f aca="false">-(G66+G71)*H42/G42</f>
@@ -15082,7 +15104,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="60" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H147" s="65" t="n">
         <f aca="false">G54*Drivers!$C$29</f>
@@ -15099,10 +15121,10 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="60" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B148" s="56" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H148" s="65" t="n">
         <f aca="false">H54-G54+H147</f>
@@ -15119,10 +15141,10 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="60" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B149" s="56" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H149" s="65" t="n">
         <f aca="false">-(G66+G71)+H148-H146</f>
@@ -15139,7 +15161,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="60" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H150" s="65" t="n">
         <f aca="false">-(G66+G71)*Drivers!$C$30</f>
@@ -15156,7 +15178,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="60" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="H151" s="65" t="n">
         <f aca="false">-G69*Drivers!$C$32</f>
@@ -15173,7 +15195,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="60" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H152" s="65" t="n">
         <f aca="false">MAX(G61,0)*Drivers!$C$31</f>
@@ -15190,7 +15212,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="60" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H153" s="65" t="n">
         <f aca="false">H7*Drivers!$C$22</f>
@@ -15207,7 +15229,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="60" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="H154" s="65" t="n">
         <f aca="false">Drivers!$C$12*Drivers!$C$13</f>
@@ -15224,7 +15246,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="60" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H155" s="65" t="n">
         <f aca="false">Drivers!$C$12*Drivers!$C$14</f>
@@ -15241,10 +15263,10 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="60" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B156" s="56" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="H156" s="65" t="n">
         <f aca="false">Drivers!$C$33*(Drivers!$C$15-H145-H144)</f>
@@ -15261,10 +15283,10 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="60" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B157" s="56" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G157" s="81" t="n">
         <v>0.69</v>
@@ -15284,10 +15306,10 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="60" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B158" s="56" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H158" s="65" t="n">
         <f aca="false">G157*Drivers!$C$34</f>
@@ -15331,12 +15353,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15352,7 +15374,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15360,7 +15382,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C4" s="71" t="s">
         <v>9</v>
@@ -15372,30 +15394,30 @@
         <v>11</v>
       </c>
       <c r="F4" s="71" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="G4" s="71" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="H4" s="71" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I4" s="71" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="J4" s="71" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="K4" s="71" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="L4" s="71" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="82" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B5" s="83"/>
       <c r="C5" s="83"/>
@@ -15414,7 +15436,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="85" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C6" s="86" t="n">
         <f aca="false">Scenarios!F7</f>
@@ -15447,15 +15469,15 @@
         <v>140</v>
       </c>
       <c r="L6" s="88" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="84" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B7" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C7" s="89" t="n">
         <v>0.63</v>
@@ -15485,15 +15507,15 @@
         <v>0.68</v>
       </c>
       <c r="L7" s="88" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="84" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C8" s="90" t="n">
         <f aca="false">Scenarios!F10</f>
@@ -15526,15 +15548,15 @@
         <v>0.05</v>
       </c>
       <c r="L8" s="88" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="84" t="s">
+        <v>443</v>
+      </c>
+      <c r="B9" s="85" t="s">
         <v>439</v>
-      </c>
-      <c r="B9" s="85" t="s">
-        <v>435</v>
       </c>
       <c r="C9" s="90" t="n">
         <f aca="false">Scenarios!F13</f>
@@ -15567,15 +15589,15 @@
         <v>0.95</v>
       </c>
       <c r="L9" s="88" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="84" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B10" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C10" s="90" t="n">
         <f aca="false">Scenarios!F16</f>
@@ -15608,7 +15630,7 @@
         <v>0.12</v>
       </c>
       <c r="L10" s="88" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15616,7 +15638,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C11" s="90" t="n">
         <f aca="false">Scenarios!F19</f>
@@ -15649,12 +15671,12 @@
         <v>0.103</v>
       </c>
       <c r="L11" s="88" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="84" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B12" s="85" t="s">
         <v>30</v>
@@ -15675,15 +15697,15 @@
       <c r="J12" s="92"/>
       <c r="K12" s="92"/>
       <c r="L12" s="88" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="84" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C13" s="89" t="n">
         <v>0.75</v>
@@ -15701,15 +15723,15 @@
       <c r="J13" s="92"/>
       <c r="K13" s="92"/>
       <c r="L13" s="88" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="84" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C14" s="89" t="n">
         <v>0.166666666666667</v>
@@ -15727,12 +15749,12 @@
       <c r="J14" s="92"/>
       <c r="K14" s="92"/>
       <c r="L14" s="88" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="84" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B15" s="85" t="s">
         <v>30</v>
@@ -15765,15 +15787,15 @@
         <v>200</v>
       </c>
       <c r="L15" s="88" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="84" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C16" s="89" t="n">
         <v>0.02</v>
@@ -15791,15 +15813,15 @@
       <c r="J16" s="92"/>
       <c r="K16" s="92"/>
       <c r="L16" s="88" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="84" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B17" s="85" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C17" s="93" t="n">
         <f aca="false">0.69*(1+C16)</f>
@@ -15820,15 +15842,15 @@
       <c r="J17" s="92"/>
       <c r="K17" s="92"/>
       <c r="L17" s="88" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="84" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B18" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C18" s="89" t="n">
         <v>0.26</v>
@@ -15858,7 +15880,7 @@
         <v>0.27</v>
       </c>
       <c r="L18" s="88" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15877,7 +15899,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="82" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B20" s="83"/>
       <c r="C20" s="83"/>
@@ -15893,10 +15915,10 @@
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="84" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B21" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C21" s="89" t="n">
         <v>0.615</v>
@@ -15914,15 +15936,15 @@
       <c r="J21" s="92"/>
       <c r="K21" s="92"/>
       <c r="L21" s="88" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="84" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B22" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C22" s="89" t="n">
         <v>0.047</v>
@@ -15940,15 +15962,15 @@
       <c r="J22" s="92"/>
       <c r="K22" s="92"/>
       <c r="L22" s="88" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="84" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B23" s="85" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C23" s="91" t="n">
         <v>25</v>
@@ -15966,15 +15988,15 @@
       <c r="J23" s="92"/>
       <c r="K23" s="92"/>
       <c r="L23" s="88" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="84" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B24" s="85" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C24" s="91" t="n">
         <v>11.5</v>
@@ -15992,15 +16014,15 @@
       <c r="J24" s="92"/>
       <c r="K24" s="92"/>
       <c r="L24" s="88" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="84" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B25" s="85" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C25" s="91" t="n">
         <v>45</v>
@@ -16018,15 +16040,15 @@
       <c r="J25" s="92"/>
       <c r="K25" s="92"/>
       <c r="L25" s="88" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="84" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B26" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C26" s="89" t="n">
         <v>0.135</v>
@@ -16044,15 +16066,15 @@
       <c r="J26" s="92"/>
       <c r="K26" s="92"/>
       <c r="L26" s="88" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="84" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B27" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C27" s="89" t="n">
         <v>0.08</v>
@@ -16070,15 +16092,15 @@
       <c r="J27" s="92"/>
       <c r="K27" s="92"/>
       <c r="L27" s="88" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="84" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B28" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C28" s="89" t="n">
         <v>0.18</v>
@@ -16096,15 +16118,15 @@
       <c r="J28" s="92"/>
       <c r="K28" s="92"/>
       <c r="L28" s="88" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="84" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B29" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C29" s="89" t="n">
         <v>0.17</v>
@@ -16122,15 +16144,15 @@
       <c r="J29" s="92"/>
       <c r="K29" s="92"/>
       <c r="L29" s="88" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="84" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B30" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C30" s="94" t="n">
         <v>0.048</v>
@@ -16148,15 +16170,15 @@
       <c r="J30" s="92"/>
       <c r="K30" s="92"/>
       <c r="L30" s="95" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="84" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B31" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C31" s="89" t="n">
         <v>0.03</v>
@@ -16174,15 +16196,15 @@
       <c r="J31" s="92"/>
       <c r="K31" s="92"/>
       <c r="L31" s="88" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="84" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B32" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C32" s="89" t="n">
         <v>0.05</v>
@@ -16200,15 +16222,15 @@
       <c r="J32" s="92"/>
       <c r="K32" s="92"/>
       <c r="L32" s="88" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="84" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B33" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C33" s="89" t="n">
         <v>0.11</v>
@@ -16226,15 +16248,15 @@
       <c r="J33" s="92"/>
       <c r="K33" s="92"/>
       <c r="L33" s="88" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="84" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B34" s="85" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C34" s="91" t="n">
         <v>101.9</v>
@@ -16252,15 +16274,15 @@
       <c r="J34" s="92"/>
       <c r="K34" s="92"/>
       <c r="L34" s="88" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="84" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B35" s="85" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C35" s="89" t="n">
         <v>0.139</v>
@@ -16278,15 +16300,15 @@
       <c r="J35" s="92"/>
       <c r="K35" s="92"/>
       <c r="L35" s="88" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="96" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B36" s="96" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C36" s="97" t="n">
         <v>0.5</v>
@@ -16304,12 +16326,12 @@
       <c r="J36" s="92"/>
       <c r="K36" s="92"/>
       <c r="L36" s="88" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="82" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B37" s="83"/>
       <c r="C37" s="83"/>
@@ -16325,10 +16347,10 @@
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="84" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B38" s="85" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C38" s="98" t="n">
         <v>0.5</v>
@@ -16342,15 +16364,15 @@
       <c r="J38" s="92"/>
       <c r="K38" s="92"/>
       <c r="L38" s="88" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="84" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B39" s="85" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C39" s="98" t="n">
         <v>0.3</v>
@@ -16364,7 +16386,7 @@
       <c r="J39" s="92"/>
       <c r="K39" s="92"/>
       <c r="L39" s="88" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16383,7 +16405,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="82" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B41" s="83"/>
       <c r="C41" s="83"/>
@@ -16399,20 +16421,20 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="99" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B42" s="99"/>
       <c r="C42" s="99" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D42" s="99" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E42" s="99" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F42" s="99" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G42" s="92"/>
       <c r="H42" s="92"/>
@@ -16423,7 +16445,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="84" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B43" s="92"/>
       <c r="C43" s="100" t="n">
@@ -16479,7 +16501,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="84" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B45" s="92"/>
       <c r="C45" s="100" t="n">
@@ -16507,7 +16529,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="84" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B46" s="92"/>
       <c r="C46" s="100" t="n">
@@ -16563,7 +16585,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="84" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B48" s="92"/>
       <c r="C48" s="101" t="n">
@@ -16591,7 +16613,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="84" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B49" s="92"/>
       <c r="C49" s="101" t="n">
@@ -16619,7 +16641,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="84" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B50" s="92"/>
       <c r="C50" s="101" t="n">
@@ -16647,7 +16669,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="84" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B51" s="92"/>
       <c r="C51" s="100" t="n">
@@ -16675,7 +16697,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="84" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B52" s="92"/>
       <c r="C52" s="101" t="n">
@@ -16717,7 +16739,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="82" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B54" s="83"/>
       <c r="C54" s="83"/>
@@ -16733,7 +16755,7 @@
     </row>
     <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="84" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B55" s="92"/>
       <c r="C55" s="91" t="n">
@@ -16748,12 +16770,12 @@
       <c r="J55" s="92"/>
       <c r="K55" s="92"/>
       <c r="L55" s="88" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="84" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B56" s="92"/>
       <c r="C56" s="91" t="n">
@@ -16768,12 +16790,12 @@
       <c r="J56" s="92"/>
       <c r="K56" s="92"/>
       <c r="L56" s="88" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="84" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B57" s="92"/>
       <c r="C57" s="89" t="n">
@@ -16788,12 +16810,12 @@
       <c r="J57" s="92"/>
       <c r="K57" s="92"/>
       <c r="L57" s="88" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="84" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B58" s="92"/>
       <c r="C58" s="87" t="n">
@@ -16808,16 +16830,16 @@
       <c r="J58" s="92"/>
       <c r="K58" s="92"/>
       <c r="L58" s="88" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="84" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B59" s="92"/>
       <c r="C59" s="102" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D59" s="92"/>
       <c r="E59" s="92"/>
@@ -16828,12 +16850,12 @@
       <c r="J59" s="92"/>
       <c r="K59" s="92"/>
       <c r="L59" s="88" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="84" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B60" s="92"/>
       <c r="C60" s="91" t="n">
@@ -16848,12 +16870,12 @@
       <c r="J60" s="92"/>
       <c r="K60" s="92"/>
       <c r="L60" s="88" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="84" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B61" s="92"/>
       <c r="C61" s="89" t="n">
@@ -16868,12 +16890,12 @@
       <c r="J61" s="92"/>
       <c r="K61" s="92"/>
       <c r="L61" s="88" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="84" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B62" s="92"/>
       <c r="C62" s="91" t="n">
@@ -16888,7 +16910,7 @@
       <c r="J62" s="92"/>
       <c r="K62" s="92"/>
       <c r="L62" s="88" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -16926,7 +16948,7 @@
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -16940,7 +16962,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="77" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B4" s="103" t="s">
         <v>41</v>
@@ -16952,7 +16974,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="104" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C6" s="104" t="s">
         <v>41</v>
@@ -16970,7 +16992,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="52" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B7" s="106" t="s">
         <v>9</v>
@@ -17453,12 +17475,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -17478,7 +17500,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="111" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -17488,7 +17510,7 @@
     </row>
     <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -17498,7 +17520,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B6" s="112" t="n">
         <f aca="false">Historical!F36</f>
@@ -17507,7 +17529,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B7" s="113" t="n">
         <f aca="false">Historical!G47</f>
@@ -17516,7 +17538,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B8" s="114" t="n">
         <f aca="false">Historical!F49</f>
@@ -17525,7 +17547,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B9" s="115" t="n">
         <f aca="false">B8*(1+B7)</f>
@@ -17534,7 +17556,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B10" s="116" t="n">
         <f aca="false">Historical!F42-Historical!E42</f>
@@ -17543,7 +17565,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B11" s="116" t="n">
         <f aca="false">Historical!G42-Historical!F42</f>
@@ -17552,7 +17574,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B12" s="113" t="n">
         <f aca="false">Scenarios!C13</f>
@@ -17561,7 +17583,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B13" s="117" t="n">
         <f aca="false">B6*(1+B7)</f>
@@ -17570,7 +17592,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B14" s="117" t="n">
         <f aca="false">B10*(1-Drivers!C36)*B9*B12</f>
@@ -17579,7 +17601,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B15" s="117" t="n">
         <f aca="false">B11*Drivers!C36*B9*B12</f>
@@ -17606,7 +17628,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="52" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B18" s="117" t="n">
         <f aca="false">B17-B16</f>
@@ -17633,10 +17655,10 @@
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="36" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -17665,16 +17687,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="77" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="119"/>
       <c r="B25" s="120" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C25" s="120" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D25" s="120" t="s">
         <v>95</v>
@@ -17683,12 +17705,12 @@
         <v>62</v>
       </c>
       <c r="F25" s="119" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="60" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B26" s="121" t="n">
         <v>2283.6</v>
@@ -17705,7 +17727,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="60" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B27" s="123" t="n">
         <v>0.026</v>
@@ -17718,7 +17740,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="60" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B28" s="107" t="n">
         <v>2844</v>
@@ -17735,7 +17757,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="60" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B29" s="121" t="n">
         <v>180.2</v>
@@ -17752,7 +17774,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -18083,12 +18105,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -18099,7 +18121,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="58" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -18113,27 +18135,27 @@
         <v>30</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D5" s="55" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F5" s="55" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G5" s="55" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="60" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B6" s="56" t="s">
         <v>86</v>
@@ -18161,10 +18183,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="60" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C7" s="68" t="n">
         <v>0.19</v>
@@ -18184,10 +18206,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="60" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C8" s="65" t="n">
         <f aca="false">-C6*C7</f>
@@ -18212,10 +18234,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="60" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C9" s="126" t="n">
         <v>2.8</v>
@@ -18235,7 +18257,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="60" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C10" s="126" t="n">
         <v>-1</v>
@@ -18255,7 +18277,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="60" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C11" s="126" t="n">
         <v>-3.6</v>
@@ -18275,7 +18297,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="60" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C12" s="126" t="n">
         <v>1.2</v>
@@ -18295,7 +18317,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="60" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C13" s="126" t="n">
         <v>0.2</v>
@@ -18315,10 +18337,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="62" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C14" s="63" t="n">
         <f aca="false">SUM(C8:C13)</f>
@@ -18343,7 +18365,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="60" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B15" s="56" t="s">
         <v>86</v>
@@ -18371,10 +18393,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C16" s="65" t="n">
         <f aca="false">C14-C15</f>
@@ -18399,10 +18421,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="60" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C17" s="64" t="n">
         <f aca="false">IF(C6=0,0,-C15/C6)</f>
@@ -18427,10 +18449,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C18" s="64" t="n">
         <f aca="false">C17-C7</f>
@@ -18455,7 +18477,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B20" s="59"/>
       <c r="C20" s="59"/>
@@ -18469,30 +18491,30 @@
         <v>30</v>
       </c>
       <c r="B21" s="54" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D21" s="55" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E21" s="55" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F21" s="55" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G21" s="55" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="60" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C22" s="126" t="n">
         <v>-18.9</v>
@@ -18512,10 +18534,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="60" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C23" s="126" t="n">
         <v>-9.2</v>
@@ -18535,10 +18557,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="62" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C24" s="63" t="n">
         <f aca="false">C22+C23</f>
@@ -18563,10 +18585,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="60" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C25" s="65" t="n">
         <f aca="false">C24-Historical!C17</f>
@@ -18591,10 +18613,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="60" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C26" s="76" t="n">
         <f aca="false">Historical!C93</f>
@@ -18619,7 +18641,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="58" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B28" s="59"/>
       <c r="C28" s="59"/>
@@ -18633,30 +18655,30 @@
         <v>30</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C29" s="55" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D29" s="55" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E29" s="55" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F29" s="55" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G29" s="55" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="60" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C30" s="126" t="n">
         <v>2.3</v>
@@ -18680,10 +18702,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="60" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C31" s="126" t="n">
         <v>9.2</v>
@@ -18703,10 +18725,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="60" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C32" s="126" t="n">
         <v>0</v>
@@ -18726,10 +18748,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="60" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C33" s="126" t="n">
         <v>-1.5</v>
@@ -18749,10 +18771,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="62" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C34" s="63" t="n">
         <f aca="false">SUM(C30:C33)</f>
@@ -18777,7 +18799,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="60" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B35" s="56" t="s">
         <v>86</v>
@@ -18805,10 +18827,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="60" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C36" s="65" t="n">
         <f aca="false">C34-C35</f>
@@ -18833,7 +18855,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="60" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B38" s="56" t="s">
         <v>86</v>
@@ -18861,7 +18883,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="60" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B39" s="56" t="s">
         <v>86</v>
@@ -18889,10 +18911,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="62" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C40" s="63" t="n">
         <f aca="false">C38-C39</f>
@@ -18917,7 +18939,7 @@
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="111" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B43" s="127"/>
       <c r="C43" s="127"/>
@@ -18928,13 +18950,13 @@
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="128" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B44" s="128" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C44" s="128" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D44" s="128"/>
       <c r="E44" s="128"/>
@@ -18943,13 +18965,13 @@
     </row>
     <row r="45" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="129" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B45" s="129" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C45" s="129" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D45" s="129"/>
       <c r="E45" s="129"/>
@@ -18958,7 +18980,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="26" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -18978,7 +19000,7 @@
     </row>
     <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="111" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B48" s="127"/>
       <c r="C48" s="127"/>
@@ -18989,10 +19011,10 @@
     </row>
     <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="128" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B49" s="128" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C49" s="128"/>
       <c r="D49" s="128"/>
@@ -19002,10 +19024,10 @@
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="130" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B50" s="129" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C50" s="129"/>
       <c r="D50" s="129"/>
@@ -19015,10 +19037,10 @@
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="130" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B51" s="129" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C51" s="129"/>
       <c r="D51" s="129"/>
@@ -19028,10 +19050,10 @@
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="130" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B52" s="129" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C52" s="129"/>
       <c r="D52" s="129"/>

--- a/model/GRG_model_v1.0.xlsx
+++ b/model/GRG_model_v1.0.xlsx
@@ -356,7 +356,7 @@
     <t xml:space="preserve">Key limitations</t>
   </si>
   <si>
-    <t xml:space="preserve">• Operating profit is a margin on revenue. Extra sales carry no operating leverage, and a sharp fall in sales would not squeeze the margin automatically, because fixed costs are not modelled separately.</t>
+    <t xml:space="preserve">• The model does not capture operating leverage because it forecasts operating profit as a margin on revenue; a sharp fall in sales would not squeeze the modelled margin automatically, because fixed costs are not modelled separately.</t>
   </si>
   <si>
     <t xml:space="preserve">• There is no separate impairment line, although recoverability of shop assets (IAS 36) is the auditor's key audit matter. FY22–FY25 margins absorbed £3–7m a year; a downside could bring larger charges than the margin allows for.</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">5. Sensitivities: effect on underlying PBT (saved, base case)</t>
   </si>
   <si>
-    <t xml:space="preserve">Margin matters far more than sales growth: one point of margin moves FY26 profit by about £23m, one point of LFL by under £2m. Part of that is real (one point of LFL is about £19m of revenue, earning the 8.8% margin) and part is the margin method: extra sales carry no operating leverage, so in practice LFL would move profit more. The simulation partly allows for this by linking LFL and margin.</t>
+    <t xml:space="preserve">Margin matters far more than sales growth: one point of margin moves FY26 profit by about £23m, one point of LFL by under £2m. Part of that is real (one point of LFL is about £19m of revenue, earning the 8.8% margin) and part is the margin method: the model does not capture operating leverage because it forecasts profit as a margin on revenue, so in practice LFL would likely move profit more. The simulation partly allows for this by linking LFL and margin.</t>
   </si>
   <si>
     <t xml:space="preserve">6. Back-test: FY25 revenue method vs actual</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">7.</t>
   </si>
   <si>
-    <t xml:space="preserve">Profit is a margin on revenue, so LFL growth carries no operating leverage outside the Monte Carlo (where LFL and margin are correlated at 0.5); each simulation run holds one draw per driver for all three years.</t>
+    <t xml:space="preserve">The model does not capture operating leverage because it forecasts profit as a margin on revenue (outside the Monte Carlo, where LFL and margin are correlated at 0.5); each simulation run holds one draw per driver for all three years.</t>
   </si>
   <si>
     <t xml:space="preserve">Data questions and how they were resolved</t>
@@ -3420,9 +3420,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>591480</xdr:colOff>
+      <xdr:colOff>591120</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>121320</xdr:rowOff>
+      <xdr:rowOff>120960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3436,7 +3436,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11466360" y="1036800"/>
-          <a:ext cx="6094800" cy="3199320"/>
+          <a:ext cx="6094440" cy="3198960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3457,9 +3457,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>591480</xdr:colOff>
+      <xdr:colOff>591120</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>6840</xdr:rowOff>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3473,7 +3473,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11466360" y="4656240"/>
-          <a:ext cx="6094800" cy="2894400"/>
+          <a:ext cx="6094440" cy="2894040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
